--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0687</v>
+        <v>0.0475</v>
       </c>
       <c r="E2">
-        <v>0.13575</v>
+        <v>0.114</v>
       </c>
       <c r="G2">
-        <v>0.06072635135135134</v>
+        <v>0.003586678052946203</v>
       </c>
       <c r="H2">
-        <v>0.06072635135135134</v>
+        <v>0.003586678052946203</v>
       </c>
       <c r="I2">
-        <v>0.004636824324324324</v>
+        <v>0.01528608027327071</v>
       </c>
       <c r="J2">
-        <v>0.004305005203269575</v>
+        <v>0.01411576302924167</v>
       </c>
       <c r="K2">
-        <v>8.56</v>
+        <v>5.159</v>
       </c>
       <c r="L2">
-        <v>0.07229729729729729</v>
+        <v>0.04405636208368915</v>
       </c>
       <c r="M2">
-        <v>4.6</v>
+        <v>4.06</v>
       </c>
       <c r="N2">
-        <v>0.03450862715678919</v>
+        <v>0.03621120228326793</v>
       </c>
       <c r="O2">
-        <v>0.5373831775700934</v>
+        <v>0.7869742198100408</v>
       </c>
       <c r="P2">
-        <v>4.6</v>
+        <v>4.06</v>
       </c>
       <c r="Q2">
-        <v>0.03450862715678919</v>
+        <v>0.03621120228326793</v>
       </c>
       <c r="R2">
-        <v>0.5373831775700934</v>
+        <v>0.7869742198100408</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.38</v>
+        <v>12.934</v>
       </c>
       <c r="V2">
-        <v>0.122880720180045</v>
+        <v>0.1153585444166964</v>
       </c>
       <c r="W2">
-        <v>0.1286746987951807</v>
+        <v>0.06091954022988506</v>
       </c>
       <c r="X2">
-        <v>0.05568914750947453</v>
+        <v>0.09346536927315291</v>
       </c>
       <c r="Y2">
-        <v>0.07298555128570619</v>
+        <v>-0.03254582904326785</v>
       </c>
       <c r="Z2">
-        <v>2.55850638546146</v>
+        <v>1.624358440837842</v>
       </c>
       <c r="AA2">
-        <v>0.008556064475007211</v>
+        <v>0.09493496042023324</v>
       </c>
       <c r="AB2">
-        <v>0.05531007448756661</v>
+        <v>0.09090461984957852</v>
       </c>
       <c r="AC2">
-        <v>-0.04681278102657715</v>
+        <v>0.004382115160045996</v>
       </c>
       <c r="AD2">
-        <v>4.5</v>
+        <v>4.658</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.5</v>
+        <v>4.658</v>
       </c>
       <c r="AG2">
-        <v>-11.88</v>
+        <v>-8.276</v>
       </c>
       <c r="AH2">
-        <v>0.03265602322206095</v>
+        <v>0.03988765007107503</v>
       </c>
       <c r="AI2">
-        <v>0.05257009345794393</v>
+        <v>0.05265775848425242</v>
       </c>
       <c r="AJ2">
-        <v>-0.09784220062592651</v>
+        <v>-0.07969646777859095</v>
       </c>
       <c r="AK2">
-        <v>-0.1716266974862756</v>
+        <v>-0.1095810603251946</v>
       </c>
       <c r="AL2">
-        <v>0.338</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.338</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="AN2">
-        <v>2.828409805153991</v>
+        <v>1.731598513011153</v>
       </c>
       <c r="AO2">
-        <v>1.624260355029586</v>
+        <v>3.254545454545455</v>
       </c>
       <c r="AP2">
-        <v>-7.467001885606536</v>
+        <v>-3.076579925650558</v>
       </c>
       <c r="AQ2">
-        <v>1.624260355029586</v>
+        <v>3.254545454545455</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0389</v>
+        <v>0.0475</v>
       </c>
       <c r="E3">
-        <v>0.217</v>
+        <v>0.333</v>
       </c>
       <c r="G3">
-        <v>0.01867875647668394</v>
+        <v>0.06798245614035088</v>
       </c>
       <c r="H3">
-        <v>0.01867875647668394</v>
+        <v>0.06798245614035088</v>
       </c>
       <c r="I3">
-        <v>0.02450777202072539</v>
+        <v>0.06710526315789474</v>
       </c>
       <c r="J3">
-        <v>0.02130447401801647</v>
+        <v>0.06221985251590515</v>
       </c>
       <c r="K3">
-        <v>2.11</v>
+        <v>3.37</v>
       </c>
       <c r="L3">
-        <v>0.05466321243523316</v>
+        <v>0.07390350877192982</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>0.03955223880597015</v>
+        <v>0.04188679245283019</v>
       </c>
       <c r="O3">
-        <v>0.5023696682464456</v>
+        <v>0.3293768545994065</v>
       </c>
       <c r="P3">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Q3">
-        <v>0.03955223880597015</v>
+        <v>0.04188679245283019</v>
       </c>
       <c r="R3">
-        <v>0.5023696682464456</v>
+        <v>0.3293768545994065</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>0.05597014925373135</v>
+        <v>0.04603773584905661</v>
       </c>
       <c r="W3">
-        <v>0.1098958333333333</v>
+        <v>0.1660098522167488</v>
       </c>
       <c r="X3">
-        <v>0.05894905425917632</v>
+        <v>0.09346536927315291</v>
       </c>
       <c r="Y3">
-        <v>0.05094677907415701</v>
+        <v>0.07254448294359586</v>
       </c>
       <c r="Z3">
-        <v>2.35265435484854</v>
+        <v>2.049438202247191</v>
       </c>
       <c r="AA3">
-        <v>0.05012206357624402</v>
+        <v>0.127515742684282</v>
       </c>
       <c r="AB3">
-        <v>0.0552020889590426</v>
+        <v>0.09090461984957852</v>
       </c>
       <c r="AC3">
-        <v>-0.005080025382798579</v>
+        <v>0.03661112283470351</v>
       </c>
       <c r="AD3">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1140495867768595</v>
+        <v>0.06690140845070422</v>
       </c>
       <c r="AI3">
-        <v>0.1446540880503145</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="AJ3">
-        <v>0.06782608695652174</v>
+        <v>0.02501839587932303</v>
       </c>
       <c r="AK3">
-        <v>0.08724832214765102</v>
+        <v>0.02896081771720613</v>
       </c>
       <c r="AL3">
-        <v>0.234</v>
+        <v>0.113</v>
       </c>
       <c r="AM3">
-        <v>0.234</v>
+        <v>0.113</v>
       </c>
       <c r="AN3">
-        <v>2.827868852459017</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="AO3">
-        <v>4.042735042735043</v>
+        <v>27.07964601769912</v>
       </c>
       <c r="AP3">
-        <v>1.598360655737705</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="AQ3">
-        <v>4.042735042735043</v>
+        <v>27.07964601769912</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09849999999999999</v>
+        <v>0.0596</v>
       </c>
       <c r="E4">
-        <v>0.0545</v>
+        <v>-0.105</v>
       </c>
       <c r="G4">
-        <v>0.1162921348314607</v>
+        <v>0.04662921348314607</v>
       </c>
       <c r="H4">
-        <v>0.1162921348314607</v>
+        <v>0.04662921348314607</v>
       </c>
       <c r="I4">
-        <v>0.005224719101123597</v>
+        <v>0.06610486891385768</v>
       </c>
       <c r="J4">
-        <v>0.004785948424503098</v>
+        <v>0.0557342885613167</v>
       </c>
       <c r="K4">
-        <v>5.34</v>
+        <v>2.65</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0.049625468164794</v>
       </c>
       <c r="M4">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="N4">
-        <v>0.03908045977011494</v>
+        <v>0.038866930171278</v>
       </c>
       <c r="O4">
-        <v>0.5730337078651686</v>
+        <v>1.113207547169812</v>
       </c>
       <c r="P4">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
-        <v>0.03908045977011494</v>
+        <v>0.038866930171278</v>
       </c>
       <c r="R4">
-        <v>0.5730337078651686</v>
+        <v>1.113207547169812</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>13.2</v>
+        <v>11.2</v>
       </c>
       <c r="V4">
-        <v>0.1685823754789272</v>
+        <v>0.147562582345191</v>
       </c>
       <c r="W4">
-        <v>0.1286746987951807</v>
+        <v>0.06091954022988506</v>
       </c>
       <c r="X4">
-        <v>0.05568914750947453</v>
+        <v>0.09086596633530895</v>
       </c>
       <c r="Y4">
-        <v>0.07298555128570619</v>
+        <v>-0.0299464261054239</v>
       </c>
       <c r="Z4">
-        <v>1.787746903247405</v>
+        <v>1.703349282296651</v>
       </c>
       <c r="AA4">
-        <v>0.008556064475007211</v>
+        <v>0.09493496042023324</v>
       </c>
       <c r="AB4">
-        <v>0.05536884550158436</v>
+        <v>0.09055284526018724</v>
       </c>
       <c r="AC4">
-        <v>-0.04681278102657715</v>
+        <v>0.004382115160045996</v>
       </c>
       <c r="AD4">
-        <v>1.05</v>
+        <v>0.928</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.05</v>
+        <v>0.928</v>
       </c>
       <c r="AG4">
-        <v>-12.15</v>
+        <v>-10.272</v>
       </c>
       <c r="AH4">
-        <v>0.01323251417769376</v>
+        <v>0.01207892955693237</v>
       </c>
       <c r="AI4">
-        <v>0.0227027027027027</v>
+        <v>0.02047299682315567</v>
       </c>
       <c r="AJ4">
-        <v>-0.1836734693877551</v>
+        <v>-0.1565185591515816</v>
       </c>
       <c r="AK4">
-        <v>-0.3676248108925869</v>
+        <v>-0.30098452883263</v>
       </c>
       <c r="AL4">
-        <v>0.104</v>
+        <v>0.091</v>
       </c>
       <c r="AM4">
-        <v>0.104</v>
+        <v>0.091</v>
       </c>
       <c r="AN4">
-        <v>1.417004048582996</v>
+        <v>0.2314214463840399</v>
       </c>
       <c r="AO4">
-        <v>2.682692307692308</v>
+        <v>38.79120879120879</v>
       </c>
       <c r="AP4">
-        <v>-16.39676113360324</v>
+        <v>-2.561596009975062</v>
       </c>
       <c r="AQ4">
-        <v>2.682692307692308</v>
+        <v>38.79120879120879</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tamkeen Insurance Company (PLSE:TPIC)</t>
+          <t>Ahlia Insurance Group Ltd. (PLSE:AIG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -989,95 +989,116 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.0425</v>
+      </c>
       <c r="G5">
-        <v>0.009810606060606061</v>
+        <v>-0.2856353591160221</v>
       </c>
       <c r="H5">
-        <v>0.009810606060606061</v>
+        <v>-0.2856353591160221</v>
       </c>
       <c r="I5">
-        <v>-0.02560606060606061</v>
+        <v>-0.2651933701657458</v>
       </c>
       <c r="J5">
-        <v>-0.02560606060606061</v>
+        <v>-0.2651933701657458</v>
       </c>
       <c r="K5">
-        <v>1.11</v>
+        <v>-0.861</v>
       </c>
       <c r="L5">
-        <v>0.04204545454545455</v>
+        <v>-0.04756906077348066</v>
       </c>
       <c r="M5">
-        <v>0.48</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.01702127659574468</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4324324324324324</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.48</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01702127659574468</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4324324324324324</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1.68</v>
+        <v>0.514</v>
       </c>
       <c r="V5">
-        <v>0.05957446808510639</v>
+        <v>0.05288065843621399</v>
+      </c>
+      <c r="W5">
+        <v>-0.04704918032786885</v>
       </c>
       <c r="X5">
-        <v>0.05531007448756661</v>
+        <v>0.09856060784528865</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1456097881731575</v>
+      </c>
+      <c r="Z5">
+        <v>0.9789075175770686</v>
+      </c>
+      <c r="AA5">
+        <v>-0.2595997836668469</v>
       </c>
       <c r="AB5">
-        <v>0.05531007448756661</v>
+        <v>0.09323418965752722</v>
+      </c>
+      <c r="AC5">
+        <v>-0.3528339733243741</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>-1.68</v>
+        <v>1.316</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.1584415584415584</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.09929462832338579</v>
       </c>
       <c r="AJ5">
-        <v>-0.06334841628959276</v>
+        <v>0.1192461036607466</v>
       </c>
       <c r="AK5">
-        <v>-0.1215629522431259</v>
+        <v>0.07345389595891941</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>-0.3910256410256411</v>
+      </c>
+      <c r="AO5">
+        <v>-13.8728323699422</v>
       </c>
       <c r="AP5">
-        <v>4.54054054054054</v>
+        <v>-0.2811965811965813</v>
+      </c>
+      <c r="AQ5">
+        <v>-13.8728323699422</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0475</v>
+        <v>0.00582</v>
       </c>
       <c r="E2">
-        <v>0.114</v>
+        <v>-0.119</v>
       </c>
       <c r="G2">
-        <v>0.003586678052946203</v>
+        <v>0.09771838331160365</v>
       </c>
       <c r="H2">
-        <v>0.003586678052946203</v>
+        <v>0.09771838331160365</v>
       </c>
       <c r="I2">
-        <v>0.01528608027327071</v>
+        <v>0.09582790091264667</v>
       </c>
       <c r="J2">
-        <v>0.01411576302924167</v>
+        <v>0.08321429224189401</v>
       </c>
       <c r="K2">
-        <v>5.159</v>
+        <v>9.91</v>
       </c>
       <c r="L2">
-        <v>0.04405636208368915</v>
+        <v>0.06460234680573664</v>
       </c>
       <c r="M2">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="N2">
-        <v>0.03621120228326793</v>
+        <v>0.03399311531841653</v>
       </c>
       <c r="O2">
-        <v>0.7869742198100408</v>
+        <v>0.3985872855701312</v>
       </c>
       <c r="P2">
-        <v>4.06</v>
+        <v>3.77</v>
       </c>
       <c r="Q2">
-        <v>0.03621120228326793</v>
+        <v>0.03244406196213426</v>
       </c>
       <c r="R2">
-        <v>0.7869742198100408</v>
+        <v>0.3804238143289607</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.1800000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.04556962025316459</v>
       </c>
       <c r="U2">
-        <v>12.934</v>
+        <v>10.72</v>
       </c>
       <c r="V2">
-        <v>0.1153585444166964</v>
+        <v>0.09225473321858864</v>
       </c>
       <c r="W2">
-        <v>0.06091954022988506</v>
+        <v>0.1088458905783992</v>
       </c>
       <c r="X2">
-        <v>0.09346536927315291</v>
+        <v>0.1124222216760776</v>
       </c>
       <c r="Y2">
-        <v>-0.03254582904326785</v>
+        <v>-0.003576331097678354</v>
       </c>
       <c r="Z2">
-        <v>1.624358440837842</v>
+        <v>1.669278314616523</v>
       </c>
       <c r="AA2">
-        <v>0.09493496042023324</v>
+        <v>0.1283534285961705</v>
       </c>
       <c r="AB2">
-        <v>0.09090461984957852</v>
+        <v>0.1095037208018298</v>
       </c>
       <c r="AC2">
-        <v>0.004382115160045996</v>
+        <v>0.01889072165340409</v>
       </c>
       <c r="AD2">
-        <v>4.658</v>
+        <v>14.096</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.658</v>
+        <v>14.096</v>
       </c>
       <c r="AG2">
-        <v>-8.276</v>
+        <v>3.375999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03988765007107503</v>
+        <v>0.1081844415791736</v>
       </c>
       <c r="AI2">
-        <v>0.05265775848425242</v>
+        <v>0.09648450334026941</v>
       </c>
       <c r="AJ2">
-        <v>-0.07969646777859095</v>
+        <v>0.02823309025222452</v>
       </c>
       <c r="AK2">
-        <v>-0.1095810603251946</v>
+        <v>0.02493795059685616</v>
       </c>
       <c r="AL2">
-        <v>0.5499999999999999</v>
+        <v>0.326</v>
       </c>
       <c r="AM2">
-        <v>0.5499999999999999</v>
+        <v>0.326</v>
       </c>
       <c r="AN2">
-        <v>1.731598513011153</v>
+        <v>0.876072094468614</v>
       </c>
       <c r="AO2">
-        <v>3.254545454545455</v>
+        <v>45.09202453987729</v>
       </c>
       <c r="AP2">
-        <v>-3.076579925650558</v>
+        <v>0.2098197638284648</v>
       </c>
       <c r="AQ2">
-        <v>3.254545454545455</v>
+        <v>45.09202453987729</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global United Insurance Company (PLSE:GUI)</t>
+          <t>Ahlia Insurance Group Ltd. (PLSE:AIG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0475</v>
+        <v>-0.0554</v>
       </c>
       <c r="E3">
-        <v>0.333</v>
+        <v>-0.0334</v>
       </c>
       <c r="G3">
-        <v>0.06798245614035088</v>
+        <v>0.07972972972972973</v>
       </c>
       <c r="H3">
-        <v>0.06798245614035088</v>
+        <v>0.07972972972972973</v>
       </c>
       <c r="I3">
-        <v>0.06710526315789474</v>
+        <v>0.1414414414414414</v>
       </c>
       <c r="J3">
-        <v>0.06221985251590515</v>
+        <v>0.1414414414414414</v>
       </c>
       <c r="K3">
-        <v>3.37</v>
+        <v>2.14</v>
       </c>
       <c r="L3">
-        <v>0.07390350877192982</v>
+        <v>0.09639639639639641</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>0.032</v>
       </c>
       <c r="N3">
-        <v>0.04188679245283019</v>
+        <v>0.003106796116504854</v>
       </c>
       <c r="O3">
-        <v>0.3293768545994065</v>
+        <v>0.01495327102803738</v>
       </c>
       <c r="P3">
-        <v>1.11</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04188679245283019</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3293768545994065</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1.22</v>
+        <v>3.31</v>
       </c>
       <c r="V3">
-        <v>0.04603773584905661</v>
+        <v>0.3213592233009708</v>
       </c>
       <c r="W3">
-        <v>0.1660098522167488</v>
+        <v>0.1289156626506024</v>
       </c>
       <c r="X3">
-        <v>0.09346536927315291</v>
+        <v>0.1691797618295912</v>
       </c>
       <c r="Y3">
-        <v>0.07254448294359586</v>
+        <v>-0.04026409917898874</v>
       </c>
       <c r="Z3">
-        <v>2.049438202247191</v>
+        <v>1.239115874079035</v>
       </c>
       <c r="AA3">
-        <v>0.127515742684282</v>
+        <v>0.1752623353427104</v>
       </c>
       <c r="AB3">
-        <v>0.09090461984957852</v>
+        <v>0.1117913704512387</v>
       </c>
       <c r="AC3">
-        <v>0.03661112283470351</v>
+        <v>0.06347096489147171</v>
       </c>
       <c r="AD3">
-        <v>1.9</v>
+        <v>10.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>10.7</v>
       </c>
       <c r="AG3">
-        <v>0.6799999999999999</v>
+        <v>7.389999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.06690140845070422</v>
+        <v>0.5095238095238095</v>
       </c>
       <c r="AI3">
-        <v>0.07692307692307693</v>
+        <v>0.1822827938671209</v>
       </c>
       <c r="AJ3">
-        <v>0.02501839587932303</v>
+        <v>0.4177501413227812</v>
       </c>
       <c r="AK3">
-        <v>0.02896081771720613</v>
+        <v>0.1334175844015165</v>
       </c>
       <c r="AL3">
-        <v>0.113</v>
+        <v>0.274</v>
       </c>
       <c r="AM3">
-        <v>0.113</v>
+        <v>0.274</v>
       </c>
       <c r="AN3">
-        <v>0.5654761904761905</v>
+        <v>3.194029850746269</v>
       </c>
       <c r="AO3">
-        <v>27.07964601769912</v>
+        <v>11.45985401459854</v>
       </c>
       <c r="AP3">
-        <v>0.2023809523809524</v>
+        <v>2.205970149253731</v>
       </c>
       <c r="AQ3">
-        <v>27.07964601769912</v>
+        <v>11.45985401459854</v>
       </c>
     </row>
     <row r="4">
@@ -856,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0596</v>
+        <v>0.00582</v>
       </c>
       <c r="E4">
-        <v>-0.105</v>
+        <v>-0.119</v>
       </c>
       <c r="G4">
-        <v>0.04662921348314607</v>
+        <v>0.1313253012048193</v>
       </c>
       <c r="H4">
-        <v>0.04662921348314607</v>
+        <v>0.1313253012048193</v>
       </c>
       <c r="I4">
-        <v>0.06610486891385768</v>
+        <v>0.1230923694779116</v>
       </c>
       <c r="J4">
-        <v>0.0557342885613167</v>
+        <v>0.08493373493975903</v>
       </c>
       <c r="K4">
-        <v>2.65</v>
+        <v>3.33</v>
       </c>
       <c r="L4">
-        <v>0.049625468164794</v>
+        <v>0.06686746987951808</v>
       </c>
       <c r="M4">
-        <v>2.95</v>
+        <v>2.328</v>
       </c>
       <c r="N4">
-        <v>0.038866930171278</v>
+        <v>0.04091388400702988</v>
       </c>
       <c r="O4">
-        <v>1.113207547169812</v>
+        <v>0.6990990990990992</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>0.038866930171278</v>
+        <v>0.03831282952548331</v>
       </c>
       <c r="R4">
-        <v>1.113207547169812</v>
+        <v>0.6546546546546547</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.1480000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.06357388316151208</v>
       </c>
       <c r="U4">
-        <v>11.2</v>
+        <v>5.71</v>
       </c>
       <c r="V4">
-        <v>0.147562582345191</v>
+        <v>0.1003514938488577</v>
       </c>
       <c r="W4">
-        <v>0.06091954022988506</v>
+        <v>0.07816901408450704</v>
       </c>
       <c r="X4">
-        <v>0.09086596633530895</v>
+        <v>0.110394231532559</v>
       </c>
       <c r="Y4">
-        <v>-0.0299464261054239</v>
+        <v>-0.03222521744805198</v>
       </c>
       <c r="Z4">
-        <v>1.703349282296651</v>
+        <v>1.540460282108389</v>
       </c>
       <c r="AA4">
-        <v>0.09493496042023324</v>
+        <v>0.1308370452858203</v>
       </c>
       <c r="AB4">
-        <v>0.09055284526018724</v>
+        <v>0.1095750664535829</v>
       </c>
       <c r="AC4">
-        <v>0.004382115160045996</v>
+        <v>0.02126197883223739</v>
       </c>
       <c r="AD4">
-        <v>0.928</v>
+        <v>0.879</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.928</v>
+        <v>0.879</v>
       </c>
       <c r="AG4">
-        <v>-10.272</v>
+        <v>-4.831</v>
       </c>
       <c r="AH4">
-        <v>0.01207892955693237</v>
+        <v>0.01521313972204434</v>
       </c>
       <c r="AI4">
-        <v>0.02047299682315567</v>
+        <v>0.02031008110168904</v>
       </c>
       <c r="AJ4">
-        <v>-0.1565185591515816</v>
+        <v>-0.09278073325779253</v>
       </c>
       <c r="AK4">
-        <v>-0.30098452883263</v>
+        <v>-0.1285900609545103</v>
       </c>
       <c r="AL4">
-        <v>0.091</v>
+        <v>0.052</v>
       </c>
       <c r="AM4">
-        <v>0.091</v>
+        <v>0.052</v>
       </c>
       <c r="AN4">
-        <v>0.2314214463840399</v>
+        <v>0.131784107946027</v>
       </c>
       <c r="AO4">
-        <v>38.79120879120879</v>
+        <v>117.8846153846154</v>
       </c>
       <c r="AP4">
-        <v>-2.561596009975062</v>
+        <v>-0.724287856071964</v>
       </c>
       <c r="AQ4">
-        <v>38.79120879120879</v>
+        <v>117.8846153846154</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ahlia Insurance Group Ltd. (PLSE:AIG)</t>
+          <t>Global United Insurance Company (PLSE:GUI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,115 +990,237 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0425</v>
+        <v>0.0279</v>
+      </c>
+      <c r="E5">
+        <v>-0.128</v>
       </c>
       <c r="G5">
-        <v>-0.2856353591160221</v>
+        <v>0.07220077220077221</v>
       </c>
       <c r="H5">
-        <v>-0.2856353591160221</v>
+        <v>0.07220077220077221</v>
       </c>
       <c r="I5">
-        <v>-0.2651933701657458</v>
+        <v>0.07220077220077221</v>
       </c>
       <c r="J5">
-        <v>-0.2651933701657458</v>
+        <v>0.05656851778347106</v>
       </c>
       <c r="K5">
-        <v>-0.861</v>
+        <v>2.51</v>
       </c>
       <c r="L5">
-        <v>-0.04756906077348066</v>
+        <v>0.04845559845559846</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04387351778656127</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.4422310756972112</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>1.11</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.04387351778656127</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.4422310756972112</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.514</v>
+        <v>0.6</v>
       </c>
       <c r="V5">
-        <v>0.05288065843621399</v>
+        <v>0.02371541501976284</v>
       </c>
       <c r="W5">
-        <v>-0.04704918032786885</v>
+        <v>0.1110619469026548</v>
       </c>
       <c r="X5">
-        <v>0.09856060784528865</v>
+        <v>0.1135028315661799</v>
       </c>
       <c r="Y5">
-        <v>-0.1456097881731575</v>
+        <v>-0.002440884663525045</v>
       </c>
       <c r="Z5">
-        <v>0.9789075175770686</v>
+        <v>2.225085910652921</v>
       </c>
       <c r="AA5">
-        <v>-0.2595997836668469</v>
+        <v>0.1258698119065207</v>
       </c>
       <c r="AB5">
-        <v>0.09323418965752722</v>
+        <v>0.1093503474319499</v>
       </c>
       <c r="AC5">
-        <v>-0.3528339733243741</v>
+        <v>0.0165194644745708</v>
       </c>
       <c r="AD5">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG5">
-        <v>1.316</v>
+        <v>1.16</v>
       </c>
       <c r="AH5">
-        <v>0.1584415584415584</v>
+        <v>0.06504065040650406</v>
       </c>
       <c r="AI5">
-        <v>0.09929462832338579</v>
+        <v>0.0728476821192053</v>
       </c>
       <c r="AJ5">
-        <v>0.1192461036607466</v>
+        <v>0.04383975812547242</v>
       </c>
       <c r="AK5">
-        <v>0.07345389595891941</v>
+        <v>0.04923599320882853</v>
       </c>
       <c r="AL5">
-        <v>0.346</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.346</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>-0.3910256410256411</v>
-      </c>
-      <c r="AO5">
-        <v>-13.8728323699422</v>
+        <v>0.4378109452736319</v>
       </c>
       <c r="AP5">
-        <v>-0.2811965811965813</v>
-      </c>
-      <c r="AQ5">
-        <v>-13.8728323699422</v>
+        <v>0.2885572139303483</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Palestinian Authority</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tamkeen Insurance Company (PLSE:TPIC)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0.09932432432432432</v>
+      </c>
+      <c r="H6">
+        <v>0.09932432432432432</v>
+      </c>
+      <c r="I6">
+        <v>0.05709459459459459</v>
+      </c>
+      <c r="J6">
+        <v>0.05709459459459459</v>
+      </c>
+      <c r="K6">
+        <v>1.93</v>
+      </c>
+      <c r="L6">
+        <v>0.0652027027027027</v>
+      </c>
+      <c r="M6">
+        <v>0.48</v>
+      </c>
+      <c r="N6">
+        <v>0.02025316455696203</v>
+      </c>
+      <c r="O6">
+        <v>0.2487046632124352</v>
+      </c>
+      <c r="P6">
+        <v>0.48</v>
+      </c>
+      <c r="Q6">
+        <v>0.02025316455696203</v>
+      </c>
+      <c r="R6">
+        <v>0.2487046632124352</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1.1</v>
+      </c>
+      <c r="V6">
+        <v>0.04641350210970464</v>
+      </c>
+      <c r="W6">
+        <v>0.1066298342541436</v>
+      </c>
+      <c r="X6">
+        <v>0.1113416117859753</v>
+      </c>
+      <c r="Y6">
+        <v>-0.004711777531831676</v>
+      </c>
+      <c r="Z6">
+        <v>1.611147398214674</v>
+      </c>
+      <c r="AA6">
+        <v>0.09198780753320268</v>
+      </c>
+      <c r="AB6">
+        <v>0.1094323751500767</v>
+      </c>
+      <c r="AC6">
+        <v>-0.01744456761687405</v>
+      </c>
+      <c r="AD6">
+        <v>0.757</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0.757</v>
+      </c>
+      <c r="AG6">
+        <v>-0.3430000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.03095228359978738</v>
+      </c>
+      <c r="AI6">
+        <v>0.03793155283860299</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.0146851051076765</v>
+      </c>
+      <c r="AK6">
+        <v>-0.01818953173887682</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0.3692682926829269</v>
+      </c>
+      <c r="AP6">
+        <v>-0.1673170731707318</v>
       </c>
     </row>
   </sheetData>
